--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/UTAH_2016.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/UTAH_2016.xlsx
@@ -427,7 +427,7 @@
         <v>11</v>
       </c>
       <c r="D4">
-        <v>0.0009317296290022023</v>
+        <v>0.0009317296290022024</v>
       </c>
     </row>
     <row r="5">
@@ -643,7 +643,7 @@
         <v>11</v>
       </c>
       <c r="D16">
-        <v>0.0009317296290022023</v>
+        <v>0.0009317296290022024</v>
       </c>
     </row>
     <row r="17">
@@ -2623,7 +2623,7 @@
         <v>113</v>
       </c>
       <c r="D126">
-        <v>0.009571404370658987</v>
+        <v>0.009571404370658988</v>
       </c>
     </row>
     <row r="127">
@@ -2677,7 +2677,7 @@
         <v>11</v>
       </c>
       <c r="D129">
-        <v>0.0009317296290022023</v>
+        <v>0.0009317296290022024</v>
       </c>
     </row>
     <row r="130">
@@ -2893,7 +2893,7 @@
         <v>11</v>
       </c>
       <c r="D141">
-        <v>0.0009317296290022023</v>
+        <v>0.0009317296290022024</v>
       </c>
     </row>
     <row r="142">
@@ -4207,7 +4207,7 @@
         <v>11</v>
       </c>
       <c r="D214">
-        <v>0.0009317296290022023</v>
+        <v>0.0009317296290022024</v>
       </c>
     </row>
     <row r="215">
@@ -4927,7 +4927,7 @@
         <v>11</v>
       </c>
       <c r="D254">
-        <v>0.0009317296290022023</v>
+        <v>0.0009317296290022024</v>
       </c>
     </row>
     <row r="255">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C264">
@@ -5395,7 +5395,7 @@
         <v>11</v>
       </c>
       <c r="D280">
-        <v>0.0009317296290022023</v>
+        <v>0.0009317296290022024</v>
       </c>
     </row>
     <row r="281">
@@ -5413,7 +5413,7 @@
         <v>11</v>
       </c>
       <c r="D281">
-        <v>0.0009317296290022023</v>
+        <v>0.0009317296290022024</v>
       </c>
     </row>
     <row r="282">
@@ -5935,7 +5935,7 @@
         <v>11</v>
       </c>
       <c r="D310">
-        <v>0.0009317296290022023</v>
+        <v>0.0009317296290022024</v>
       </c>
     </row>
     <row r="311">
@@ -6223,7 +6223,7 @@
         <v>11</v>
       </c>
       <c r="D326">
-        <v>0.0009317296290022023</v>
+        <v>0.0009317296290022024</v>
       </c>
     </row>
     <row r="327">
@@ -6475,7 +6475,7 @@
         <v>108</v>
       </c>
       <c r="D340">
-        <v>0.009147890902930713</v>
+        <v>0.009147890902930712</v>
       </c>
     </row>
     <row r="341">
@@ -7843,7 +7843,7 @@
         <v>11</v>
       </c>
       <c r="D416">
-        <v>0.0009317296290022023</v>
+        <v>0.0009317296290022024</v>
       </c>
     </row>
     <row r="417">
@@ -9931,7 +9931,7 @@
         <v>11</v>
       </c>
       <c r="D532">
-        <v>0.0009317296290022023</v>
+        <v>0.0009317296290022024</v>
       </c>
     </row>
     <row r="533">
@@ -10165,7 +10165,7 @@
         <v>11</v>
       </c>
       <c r="D545">
-        <v>0.0009317296290022023</v>
+        <v>0.0009317296290022024</v>
       </c>
     </row>
     <row r="546">
@@ -11587,7 +11587,7 @@
         <v>11</v>
       </c>
       <c r="D624">
-        <v>0.0009317296290022023</v>
+        <v>0.0009317296290022024</v>
       </c>
     </row>
     <row r="625">
@@ -11767,7 +11767,7 @@
         <v>11</v>
       </c>
       <c r="D634">
-        <v>0.0009317296290022023</v>
+        <v>0.0009317296290022024</v>
       </c>
     </row>
     <row r="635">
@@ -13272,7 +13272,7 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec -Distrito 08-</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C718">
@@ -14305,7 +14305,7 @@
         <v>11</v>
       </c>
       <c r="D775">
-        <v>0.0009317296290022023</v>
+        <v>0.0009317296290022024</v>
       </c>
     </row>
     <row r="776">
@@ -18157,7 +18157,7 @@
         <v>11</v>
       </c>
       <c r="D989">
-        <v>0.0009317296290022023</v>
+        <v>0.0009317296290022024</v>
       </c>
     </row>
     <row r="990">
@@ -18445,7 +18445,7 @@
         <v>11</v>
       </c>
       <c r="D1005">
-        <v>0.0009317296290022023</v>
+        <v>0.0009317296290022024</v>
       </c>
     </row>
     <row r="1006">
@@ -18787,7 +18787,7 @@
         <v>11</v>
       </c>
       <c r="D1024">
-        <v>0.0009317296290022023</v>
+        <v>0.0009317296290022024</v>
       </c>
     </row>
     <row r="1025">
@@ -19093,7 +19093,7 @@
         <v>11</v>
       </c>
       <c r="D1041">
-        <v>0.0009317296290022023</v>
+        <v>0.0009317296290022024</v>
       </c>
     </row>
     <row r="1042">
@@ -21505,7 +21505,7 @@
         <v>11</v>
       </c>
       <c r="D1175">
-        <v>0.0009317296290022023</v>
+        <v>0.0009317296290022024</v>
       </c>
     </row>
     <row r="1176">
